--- a/report_forms/026_vehicle_take_over_report_form_template--report_forms.xlsx
+++ b/report_forms/026_vehicle_take_over_report_form_template--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Additional Remarks</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Remarks Vehicles Returned</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Additional Remarks</t>
+          <t>Remarks Returned</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Remarks Returned Vehicle</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fuel Consumed</t>
+          <t>Fuel Consumption Returned</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Additional Remarks</t>
+          <t>Remarks Returned Fuel</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>remarks_returned_vehicle</t>
+          <t>remarks_returned_vehicle_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Remarks Returned Vehicle 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>remarks_returned_vehicle_status</t>
+          <t>remarks_returned_vehicle_status_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Additional Remarks</t>
+          <t>Remarks Returned Vehicle Status 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'vehicle_in_good_condition'}</t>
+          <t>vehicle_in_good_condition</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Vehicle in Good Condition'}</t>
+          <t>Vehicle in Good Condition</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'vehicle_damaged'}</t>
+          <t>vehicle_damaged</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Vehicle Damaged'}</t>
+          <t>Vehicle Damaged</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'vehicle_not_returned'}</t>
+          <t>vehicle_not_returned</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Vehicle Not Returned'}</t>
+          <t>Vehicle Not Returned</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'vehicle_in_good_condition'}</t>
+          <t>vehicle_in_good_condition</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Vehicle in Good Condition'}</t>
+          <t>Vehicle in Good Condition</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'vehicle_damaged'}</t>
+          <t>vehicle_damaged</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Vehicle Damaged'}</t>
+          <t>Vehicle Damaged</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'vehicle_not_returned'}</t>
+          <t>vehicle_not_returned</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Vehicle Not Returned'}</t>
+          <t>Vehicle Not Returned</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'vehicle_is_returned'}</t>
+          <t>vehicle_is_returned</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Vehicle is Returned'}</t>
+          <t>Vehicle is Returned</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'vehicle_not_returned'}</t>
+          <t>vehicle_not_returned</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Vehicle Not Returned'}</t>
+          <t>Vehicle Not Returned</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'vehicle_lost'}</t>
+          <t>vehicle_lost</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Vehicle Lost'}</t>
+          <t>Vehicle Lost</t>
         </is>
       </c>
     </row>
